--- a/KiCAD/THRValveControlModule/THRValveControlModule.xlsx
+++ b/KiCAD/THRValveControlModule/THRValveControlModule.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\TSRP\H-62-Avionics\KiCAD\THRValveControlModule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7D78B041-5F44-4634-9E52-28160A18E683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{81449C4D-1F68-4FA3-8926-34E0D0BF9FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="3330" windowWidth="29040" windowHeight="15720" xr2:uid="{8CA50417-0271-44AA-A488-B542925077FF}"/>
   </bookViews>
   <sheets>
     <sheet name="THRValveControlModule" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="145">
   <si>
     <t>Reference</t>
   </si>
@@ -115,9 +116,6 @@
     <t>J4</t>
   </si>
   <si>
-    <t>XT30PW-M</t>
-  </si>
-  <si>
     <t>Connector_AMASS:AMASS_XT30PW-M_1x02_P2.50mm_Horizontal</t>
   </si>
   <si>
@@ -170,9 +168,6 @@
   </si>
   <si>
     <t>J1</t>
-  </si>
-  <si>
-    <t>B4B-XH-A(LF)(SN)</t>
   </si>
   <si>
     <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
@@ -470,6 +465,39 @@
     <rPh sb="0" eb="2">
       <t>ゴウケイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>在庫フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>〇</t>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>✕</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>購入</t>
+    <rPh sb="0" eb="2">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>XT30PW-M</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>B4B-XH-A(LF)(SN)</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -480,7 +508,7 @@
   <numFmts count="1">
     <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +665,12 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1066,7 +1100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1084,6 +1118,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1463,847 +1506,985 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2A155E-6872-4292-8191-67DFBF4E3942}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="17.7265625" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="88.08984375" customWidth="1"/>
-    <col min="6" max="6" width="68.90625" customWidth="1"/>
-    <col min="7" max="7" width="17.7265625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.1796875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" style="6" customWidth="1"/>
+    <col min="2" max="4" width="17.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="88.08984375" customWidth="1"/>
+    <col min="7" max="7" width="68.90625" customWidth="1"/>
+    <col min="8" max="8" width="17.7265625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1320</v>
+      </c>
+      <c r="I2" s="3">
+        <f>H2*C2</f>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I31" si="0">H3*C3</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2354</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="3">
+        <v>60</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="3">
+        <v>180</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="3">
+        <v>70</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="3">
+        <v>160</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="3">
+        <v>160</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="3">
+        <v>60</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="3">
+        <v>10</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="3">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="3">
+        <v>580</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" s="3">
+        <v>240</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="3">
+        <v>100</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="3">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="3">
+        <v>330</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="3">
+        <v>60</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" s="3">
+        <v>110</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="H22" s="3">
+        <v>150</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="3">
+        <v>150</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8">
+        <v>120</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1320</v>
-      </c>
-      <c r="H2" s="3">
-        <f>G2*B2</f>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H3" s="3">
-        <f t="shared" ref="H3:H31" si="0">G3*B3</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2354</v>
-      </c>
-      <c r="H4" s="3">
-        <f t="shared" si="0"/>
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H5" s="3">
-        <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="3">
-        <v>60</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="3">
-        <v>180</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="3">
-        <v>70</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G9" s="3">
-        <v>160</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="0"/>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="3">
-        <v>160</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="3">
-        <v>60</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" s="3">
-        <v>100</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="3">
-        <v>10</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G14" s="3">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G15" s="3">
-        <v>580</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="0"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="3">
-        <v>240</v>
-      </c>
-      <c r="H16" s="3">
-        <f t="shared" si="0"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="3">
-        <v>100</v>
-      </c>
-      <c r="H17" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="3">
-        <v>100</v>
-      </c>
-      <c r="H18" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="3">
-        <v>330</v>
-      </c>
-      <c r="H19" s="3">
-        <f t="shared" si="0"/>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="3">
-        <v>60</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="3">
-        <v>110</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="F32" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" s="3">
-        <v>150</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G23" s="3">
-        <v>150</v>
-      </c>
-      <c r="H23" s="3">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>120</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H26" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H27" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" t="s">
-        <v>97</v>
-      </c>
-      <c r="H28" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>106</v>
-      </c>
-      <c r="H29" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32">
-        <v>6</v>
-      </c>
-      <c r="C32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H32" s="3">
-        <f>SUM(H2:H31)</f>
+      <c r="I32" s="3">
+        <f>SUM(I2:I31)</f>
         <v>8574</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{BE64EA40-DFD2-4A3B-BC6D-576103176ED3}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{6E93B1C6-91AE-4536-99BC-5B25D8F393D3}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{09A9D408-E160-4E9E-86C3-8FC8FED54C6B}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{1581A95B-93FA-4CF3-B642-B744E75D68B7}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{4D661375-8DF7-46A4-8AD7-154168DE4924}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{6870BDDF-7C45-4FEE-8645-FFF68AF8103A}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{8FFA0D41-2D91-4D64-AAF4-15CAAE616E59}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{0CA6F6E2-5F5C-4CC3-B8EE-FC1E56831085}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{9E53063B-01CC-4128-90E0-E5704D491BDD}"/>
-    <hyperlink ref="F10" r:id="rId10" xr:uid="{827D4EE3-D37B-4217-B937-FCDD5F76F4FA}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{1AFB2CC0-9253-495B-8346-D7693912AECE}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{B7BDF868-7253-4271-AD12-768E7FE2EDE4}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{42341E44-57A0-4C67-AED2-8FF4866B2A41}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{ADBBBA6A-AD16-447C-9EE4-8417975E0E5B}"/>
-    <hyperlink ref="F16" r:id="rId15" xr:uid="{0FECF159-F014-4F8E-AEAD-7A85A15B0E47}"/>
-    <hyperlink ref="F17" r:id="rId16" xr:uid="{080A950C-871F-49BC-9A36-92AD50C04B4C}"/>
-    <hyperlink ref="F18" r:id="rId17" xr:uid="{EF0CC8B1-0B00-4EDF-948C-22FA21D8048B}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{57B8B5A5-6BA0-412A-B535-CF7E6C0A3BBD}"/>
-    <hyperlink ref="F20" r:id="rId19" xr:uid="{95860CF4-8DCC-42EE-B0B8-881034F16E25}"/>
-    <hyperlink ref="F21" r:id="rId20" xr:uid="{E2C30406-636B-46FF-8713-5E33A8CF2452}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{3B565C8F-7D23-431E-98B6-46CD619B0A42}"/>
-    <hyperlink ref="F22" r:id="rId22" xr:uid="{8E3BA8B5-27DD-48CB-91F1-A8353B994D78}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{BE64EA40-DFD2-4A3B-BC6D-576103176ED3}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{6E93B1C6-91AE-4536-99BC-5B25D8F393D3}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{09A9D408-E160-4E9E-86C3-8FC8FED54C6B}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{1581A95B-93FA-4CF3-B642-B744E75D68B7}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{4D661375-8DF7-46A4-8AD7-154168DE4924}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{6870BDDF-7C45-4FEE-8645-FFF68AF8103A}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{8FFA0D41-2D91-4D64-AAF4-15CAAE616E59}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{0CA6F6E2-5F5C-4CC3-B8EE-FC1E56831085}"/>
+    <hyperlink ref="G11" r:id="rId9" xr:uid="{9E53063B-01CC-4128-90E0-E5704D491BDD}"/>
+    <hyperlink ref="G10" r:id="rId10" xr:uid="{827D4EE3-D37B-4217-B937-FCDD5F76F4FA}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{1AFB2CC0-9253-495B-8346-D7693912AECE}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{B7BDF868-7253-4271-AD12-768E7FE2EDE4}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{42341E44-57A0-4C67-AED2-8FF4866B2A41}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{ADBBBA6A-AD16-447C-9EE4-8417975E0E5B}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{0FECF159-F014-4F8E-AEAD-7A85A15B0E47}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{080A950C-871F-49BC-9A36-92AD50C04B4C}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{EF0CC8B1-0B00-4EDF-948C-22FA21D8048B}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{57B8B5A5-6BA0-412A-B535-CF7E6C0A3BBD}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{95860CF4-8DCC-42EE-B0B8-881034F16E25}"/>
+    <hyperlink ref="G21" r:id="rId20" xr:uid="{E2C30406-636B-46FF-8713-5E33A8CF2452}"/>
+    <hyperlink ref="G23" r:id="rId21" xr:uid="{3B565C8F-7D23-431E-98B6-46CD619B0A42}"/>
+    <hyperlink ref="G22" r:id="rId22" xr:uid="{8E3BA8B5-27DD-48CB-91F1-A8353B994D78}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0D81C52-F85F-44EC-AEB3-722748EF2DA2}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$1:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A32</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B08DED-883C-40A0-8C39-0E7EB742CE8F}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>